--- a/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_2.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1753960290_h_2.xlsx
@@ -652,13 +652,13 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.01182880555700028</v>
+        <v>0.004762525672134421</v>
       </c>
       <c r="B2" t="n">
-        <v>0.008421866602520764</v>
+        <v>0.008412105359976642</v>
       </c>
       <c r="C2" t="n">
-        <v>12592554</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>12592554</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>9400355</v>
+        <v>4802236</v>
       </c>
       <c r="L2" t="n">
-        <v>5686832</v>
+        <v>2976057</v>
       </c>
       <c r="M2" t="n">
-        <v>1487003</v>
+        <v>780023</v>
       </c>
       <c r="N2" t="n">
-        <v>84043</v>
+        <v>44659</v>
       </c>
       <c r="O2" t="n">
-        <v>877898</v>
+        <v>459073</v>
       </c>
       <c r="P2" t="n">
-        <v>346370</v>
+        <v>179046</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999980926513672</v>
+        <v>0.9999983906745911</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9372426867485046</v>
+        <v>0.9557753801345825</v>
       </c>
       <c r="S2" t="n">
-        <v>0.863659679889679</v>
+        <v>0.8941516876220703</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8123999238014221</v>
+        <v>0.867652416229248</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6440224647521973</v>
+        <v>0.7122306823730469</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8591117858886719</v>
+        <v>0.8997268080711365</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9041195511817932</v>
+        <v>0.9331582188606262</v>
       </c>
       <c r="X2" t="n">
-        <v>12592554</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,43 +742,43 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>12592554</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>9612236</v>
+        <v>4820894</v>
       </c>
       <c r="AG2" t="n">
-        <v>5914772</v>
+        <v>2966404</v>
       </c>
       <c r="AH2" t="n">
-        <v>1596616</v>
+        <v>799301</v>
       </c>
       <c r="AI2" t="n">
-        <v>117783</v>
+        <v>58971</v>
       </c>
       <c r="AJ2" t="n">
-        <v>917498</v>
+        <v>458916</v>
       </c>
       <c r="AK2" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.956666111946106</v>
+        <v>0.9567357897758484</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9112259149551392</v>
+        <v>0.9112488627433777</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8582807779312134</v>
+        <v>0.8582139611244202</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.662726104259491</v>
+        <v>0.6625582575798035</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9020707607269287</v>
+        <v>0.9019841551780701</v>
       </c>
       <c r="AR2" t="n">
         <v>0.931419849395752</v>
@@ -786,270 +786,270 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.002767074797495458</v>
+        <v>0.001082796833801166</v>
       </c>
       <c r="B3" t="n">
-        <v>0.002020252121303941</v>
+        <v>0.002017379093236049</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>9400355</v>
+        <v>4802236</v>
       </c>
       <c r="E3" t="n">
-        <v>618707</v>
+        <v>228883</v>
       </c>
       <c r="F3" t="n">
-        <v>15481</v>
+        <v>2466</v>
       </c>
       <c r="G3" t="n">
-        <v>2416</v>
+        <v>482</v>
       </c>
       <c r="H3" t="n">
-        <v>333</v>
+        <v>62</v>
       </c>
       <c r="I3" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="J3" t="n">
-        <v>19980222</v>
+        <v>10016612</v>
       </c>
       <c r="K3" t="n">
-        <v>21906029</v>
+        <v>11073258</v>
       </c>
       <c r="L3" t="n">
-        <v>25175306</v>
+        <v>12717946</v>
       </c>
       <c r="M3" t="n">
-        <v>30368199</v>
+        <v>15278807</v>
       </c>
       <c r="N3" t="n">
-        <v>32348482</v>
+        <v>16222492</v>
       </c>
       <c r="O3" t="n">
-        <v>31411294</v>
+        <v>15769464</v>
       </c>
       <c r="P3" t="n">
-        <v>32149523</v>
+        <v>16123493</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9365395903587341</v>
+        <v>0.9539341330528259</v>
       </c>
       <c r="S3" t="n">
-        <v>0.874930739402771</v>
+        <v>0.9130821228027344</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7989395260810852</v>
+        <v>0.8371034264564514</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4725126922130585</v>
+        <v>0.5014259219169617</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8627676367759705</v>
+        <v>0.9019594192504883</v>
       </c>
       <c r="W3" t="n">
-        <v>0.896066427230835</v>
+        <v>0.9263459444046021</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>9612236</v>
+        <v>4820894</v>
       </c>
       <c r="Z3" t="n">
-        <v>394430</v>
+        <v>197858</v>
       </c>
       <c r="AA3" t="n">
-        <v>16993</v>
+        <v>8531</v>
       </c>
       <c r="AB3" t="n">
-        <v>13519</v>
+        <v>6780</v>
       </c>
       <c r="AC3" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="AD3" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>19980246</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>22100069</v>
+        <v>11077458</v>
       </c>
       <c r="AG3" t="n">
-        <v>25496816</v>
+        <v>12781334</v>
       </c>
       <c r="AH3" t="n">
-        <v>30447946</v>
+        <v>15265735</v>
       </c>
       <c r="AI3" t="n">
-        <v>32334994</v>
+        <v>16210502</v>
       </c>
       <c r="AJ3" t="n">
-        <v>31455659</v>
+        <v>15770758</v>
       </c>
       <c r="AK3" t="n">
-        <v>32159747</v>
+        <v>16123064</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9576488733291626</v>
+        <v>0.9576404094696045</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9099997878074646</v>
+        <v>0.9101204872131348</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8578325510025024</v>
+        <v>0.8577921390533447</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6622081995010376</v>
+        <v>0.6621193885803223</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9016851186752319</v>
+        <v>0.9016509652137756</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.9313740730285645</v>
+        <v>0.931328296661377</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.03917819090983143</v>
+        <v>0.02005585382082987</v>
       </c>
       <c r="B4" t="n">
-        <v>0.03187636554403791</v>
+        <v>0.03184710126109398</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>593543</v>
+        <v>207810</v>
       </c>
       <c r="E4" t="n">
-        <v>5686832</v>
+        <v>2976057</v>
       </c>
       <c r="F4" t="n">
-        <v>207161</v>
+        <v>73207</v>
       </c>
       <c r="G4" t="n">
-        <v>4544</v>
+        <v>1067</v>
       </c>
       <c r="H4" t="n">
-        <v>7266</v>
+        <v>1167</v>
       </c>
       <c r="I4" t="n">
-        <v>405</v>
+        <v>45</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="K4" t="n">
-        <v>629443</v>
+        <v>222204</v>
       </c>
       <c r="L4" t="n">
-        <v>897743</v>
+        <v>352301</v>
       </c>
       <c r="M4" t="n">
-        <v>343380</v>
+        <v>118981</v>
       </c>
       <c r="N4" t="n">
-        <v>46454</v>
+        <v>18044</v>
       </c>
       <c r="O4" t="n">
-        <v>143969</v>
+        <v>51163</v>
       </c>
       <c r="P4" t="n">
-        <v>36732</v>
+        <v>12825</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999990463256836</v>
+        <v>0.9999992251396179</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9368910193443298</v>
+        <v>0.954853892326355</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8692586421966553</v>
+        <v>0.9035177230834961</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8056135177612305</v>
+        <v>0.8521041870117188</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5450948476791382</v>
+        <v>0.5885205268859863</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8609358072280884</v>
+        <v>0.9008417129516602</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9000749588012695</v>
+        <v>0.9297395944595337</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>406497</v>
+        <v>203532</v>
       </c>
       <c r="Z4" t="n">
-        <v>5914772</v>
+        <v>2966404</v>
       </c>
       <c r="AA4" t="n">
-        <v>165124</v>
+        <v>82724</v>
       </c>
       <c r="AB4" t="n">
-        <v>10938</v>
+        <v>5477</v>
       </c>
       <c r="AC4" t="n">
-        <v>2284</v>
+        <v>1148</v>
       </c>
       <c r="AD4" t="n">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>435403</v>
+        <v>218004</v>
       </c>
       <c r="AG4" t="n">
-        <v>576233</v>
+        <v>288913</v>
       </c>
       <c r="AH4" t="n">
-        <v>263633</v>
+        <v>132053</v>
       </c>
       <c r="AI4" t="n">
-        <v>59942</v>
+        <v>30034</v>
       </c>
       <c r="AJ4" t="n">
-        <v>99604</v>
+        <v>49869</v>
       </c>
       <c r="AK4" t="n">
-        <v>26508</v>
+        <v>13254</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9571572542190552</v>
+        <v>0.9571878910064697</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9106124639511108</v>
+        <v>0.9106842875480652</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8580566048622131</v>
+        <v>0.8580030798912048</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6624670624732971</v>
+        <v>0.6623387336730957</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9018778800964355</v>
+        <v>0.9018175005912781</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9313969612121582</v>
+        <v>0.9313740730285645</v>
       </c>
     </row>
     <row r="5">
@@ -1059,152 +1059,152 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>20449</v>
+        <v>8140</v>
       </c>
       <c r="E5" t="n">
-        <v>248544</v>
+        <v>105286</v>
       </c>
       <c r="F5" t="n">
-        <v>1487003</v>
+        <v>780023</v>
       </c>
       <c r="G5" t="n">
-        <v>21166</v>
+        <v>8605</v>
       </c>
       <c r="H5" t="n">
-        <v>81117</v>
+        <v>29187</v>
       </c>
       <c r="I5" t="n">
-        <v>2942</v>
+        <v>571</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>636973</v>
+        <v>231902</v>
       </c>
       <c r="L5" t="n">
-        <v>812919</v>
+        <v>283296</v>
       </c>
       <c r="M5" t="n">
-        <v>374218</v>
+        <v>151789</v>
       </c>
       <c r="N5" t="n">
-        <v>93821</v>
+        <v>44405</v>
       </c>
       <c r="O5" t="n">
-        <v>139639</v>
+        <v>49900</v>
       </c>
       <c r="P5" t="n">
-        <v>40175</v>
+        <v>14236</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999992847442627</v>
+        <v>0.9999994039535522</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9611204266548157</v>
+        <v>0.9721912145614624</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9474818706512451</v>
+        <v>0.9610769748687744</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9779694080352783</v>
+        <v>0.9834184646606445</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9956935048103333</v>
+        <v>0.9961757063865662</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9912931323051453</v>
+        <v>0.9938110709190369</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9976389408111572</v>
+        <v>0.9983428120613098</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>15948</v>
+        <v>7983</v>
       </c>
       <c r="Z5" t="n">
-        <v>169377</v>
+        <v>84824</v>
       </c>
       <c r="AA5" t="n">
-        <v>1596616</v>
+        <v>799301</v>
       </c>
       <c r="AB5" t="n">
-        <v>19836</v>
+        <v>9943</v>
       </c>
       <c r="AC5" t="n">
-        <v>58178</v>
+        <v>29128</v>
       </c>
       <c r="AD5" t="n">
-        <v>1266</v>
+        <v>633</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>425092</v>
+        <v>213244</v>
       </c>
       <c r="AG5" t="n">
-        <v>584979</v>
+        <v>292949</v>
       </c>
       <c r="AH5" t="n">
-        <v>264605</v>
+        <v>132511</v>
       </c>
       <c r="AI5" t="n">
-        <v>60081</v>
+        <v>30093</v>
       </c>
       <c r="AJ5" t="n">
-        <v>100039</v>
+        <v>50057</v>
       </c>
       <c r="AK5" t="n">
-        <v>26527</v>
+        <v>13273</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.97358238697052</v>
+        <v>0.9735910296440125</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9643502831459045</v>
+        <v>0.9643676280975342</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9837828278541565</v>
+        <v>0.9837985038757324</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9963152408599854</v>
+        <v>0.9963179230690002</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938708543777466</v>
+        <v>0.9938806891441345</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983717799186707</v>
+        <v>0.9983755350112915</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D6" t="n">
-        <v>15368</v>
+        <v>6224</v>
       </c>
       <c r="E6" t="n">
-        <v>24127</v>
+        <v>17227</v>
       </c>
       <c r="F6" t="n">
-        <v>35434</v>
+        <v>13359</v>
       </c>
       <c r="G6" t="n">
-        <v>84043</v>
+        <v>44659</v>
       </c>
       <c r="H6" t="n">
-        <v>17670</v>
+        <v>7198</v>
       </c>
       <c r="I6" t="n">
-        <v>1215</v>
+        <v>394</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>12847</v>
+        <v>6433</v>
       </c>
       <c r="Z6" t="n">
-        <v>10646</v>
+        <v>5341</v>
       </c>
       <c r="AA6" t="n">
-        <v>21693</v>
+        <v>10859</v>
       </c>
       <c r="AB6" t="n">
-        <v>117783</v>
+        <v>58971</v>
       </c>
       <c r="AC6" t="n">
-        <v>13933</v>
+        <v>6979</v>
       </c>
       <c r="AD6" t="n">
-        <v>962</v>
+        <v>481</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1263,22 +1263,22 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>6021</v>
+        <v>801</v>
       </c>
       <c r="F7" t="n">
-        <v>83773</v>
+        <v>29621</v>
       </c>
       <c r="G7" t="n">
-        <v>17664</v>
+        <v>7650</v>
       </c>
       <c r="H7" t="n">
-        <v>877898</v>
+        <v>459073</v>
       </c>
       <c r="I7" t="n">
-        <v>32136</v>
+        <v>11806</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="Z7" t="n">
-        <v>1618</v>
+        <v>809</v>
       </c>
       <c r="AA7" t="n">
-        <v>59163</v>
+        <v>29609</v>
       </c>
       <c r="AB7" t="n">
-        <v>15119</v>
+        <v>7569</v>
       </c>
       <c r="AC7" t="n">
-        <v>917498</v>
+        <v>458916</v>
       </c>
       <c r="AD7" t="n">
-        <v>24084</v>
+        <v>12042</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
-        <v>344</v>
+        <v>104</v>
       </c>
       <c r="F8" t="n">
-        <v>1531</v>
+        <v>328</v>
       </c>
       <c r="G8" t="n">
-        <v>664</v>
+        <v>240</v>
       </c>
       <c r="H8" t="n">
-        <v>37583</v>
+        <v>13549</v>
       </c>
       <c r="I8" t="n">
-        <v>346370</v>
+        <v>179046</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="AA8" t="n">
-        <v>660</v>
+        <v>330</v>
       </c>
       <c r="AB8" t="n">
-        <v>530</v>
+        <v>265</v>
       </c>
       <c r="AC8" t="n">
-        <v>25119</v>
+        <v>12569</v>
       </c>
       <c r="AD8" t="n">
-        <v>360018</v>
+        <v>180009</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
